--- a/www/flightdata/xlsx/eoss-376.xlsx
+++ b/www/flightdata/xlsx/eoss-376.xlsx
@@ -3555,7 +3555,7 @@
         <v>28522.27</v>
       </c>
       <c r="I2">
-        <v>720</v>
+        <v>456</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
